--- a/data/fmsForecastOutput/File1/RPT_RPT7156946910381YQ_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT7156946910381YQ_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>33.24301493444693</v>
+        <v>33.24301493444691</v>
       </c>
       <c r="D8" s="149" t="n">
         <v>12.38462060959148</v>
@@ -1884,13 +1884,13 @@
         <v>11.16597918764814</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>9.109498034422586</v>
+        <v>9.109498034422584</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>7.737317135895518</v>
+        <v>7.737317135895514</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>32.73593038944852</v>
+        <v>32.7359303894485</v>
       </c>
       <c r="I8" s="149" t="n">
         <v>12.08020833942218</v>
@@ -1899,25 +1899,25 @@
         <v>10.74536453089184</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>8.777883831876805</v>
+        <v>8.777883831876803</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>7.480316261491202</v>
+        <v>7.480316261491198</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>29966.17347643992</v>
+        <v>29966.1734764399</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>23852.46668286989</v>
+        <v>23852.46668286988</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>25213.05451676014</v>
+        <v>25213.05451676013</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>24301.92188076144</v>
+        <v>24301.92188076143</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>24510.74857133398</v>
+        <v>24510.74857133396</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1925,22 +1925,22 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>34.81812038021872</v>
+        <v>34.81812038021869</v>
       </c>
       <c r="U8" s="149" t="n">
         <v>12.97142308236514</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>11.69504054566638</v>
+        <v>11.69504054566637</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>9.541120135804203</v>
+        <v>9.541120135804201</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>8.103923184728471</v>
+        <v>8.103923184728467</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>34.26224628437447</v>
+        <v>34.26224628437446</v>
       </c>
       <c r="Z8" s="149" t="n">
         <v>12.63786882320594</v>
@@ -1949,25 +1949,25 @@
         <v>11.23444494365821</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>9.177963055026286</v>
+        <v>9.177963055026284</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>7.822434154386021</v>
+        <v>7.822434154386018</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>29966.17347643992</v>
+        <v>29966.1734764399</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>23852.46668286989</v>
+        <v>23852.46668286988</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>25213.05451676014</v>
+        <v>25213.05451676013</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>24301.92188076144</v>
+        <v>24301.92188076143</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>24510.74857133398</v>
+        <v>24510.74857133396</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2022,13 +2022,13 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>148.647768723232</v>
+        <v>148.6477687232319</v>
       </c>
       <c r="D9" s="156" t="n">
         <v>119.8607365928716</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>136.3692037973394</v>
+        <v>136.3692037973393</v>
       </c>
       <c r="F9" s="156" t="n">
         <v>143.1217395074897</v>
@@ -2043,7 +2043,7 @@
         <v>93.80534373777257</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>99.19872792547044</v>
+        <v>99.19872792547042</v>
       </c>
       <c r="K9" s="156" t="n">
         <v>104.0536929654512</v>
@@ -2081,19 +2081,19 @@
         <v>137.0293295496375</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>143.8145524251555</v>
+        <v>143.8145524251556</v>
       </c>
       <c r="X9" s="157" t="n">
         <v>143.2627860192755</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>126.7693327954454</v>
+        <v>126.7693327954453</v>
       </c>
       <c r="Z9" s="156" t="n">
         <v>94.16034657816169</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>99.54757382350682</v>
+        <v>99.54757382350681</v>
       </c>
       <c r="AB9" s="156" t="n">
         <v>104.4194109129287</v>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>49.78212053985677</v>
+        <v>49.78212053985676</v>
       </c>
       <c r="D10" s="162" t="n">
         <v>21.38731608872115</v>
@@ -2185,13 +2185,13 @@
         <v>16.37338026002993</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>47.92759239537334</v>
+        <v>47.92759239537332</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>20.43982926559778</v>
+        <v>20.43982926559777</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>19.11615207388864</v>
+        <v>19.11615207388863</v>
       </c>
       <c r="K10" s="162" t="n">
         <v>17.18419223571832</v>
@@ -2200,19 +2200,19 @@
         <v>15.51653852999623</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>52382.058043266</v>
+        <v>52382.05804326598</v>
       </c>
       <c r="N10" s="165" t="n">
         <v>44957.25837037079</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>49542.86344087819</v>
+        <v>49542.86344087817</v>
       </c>
       <c r="P10" s="165" t="n">
         <v>52178.93781677113</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>55418.07027748255</v>
+        <v>55418.07027748253</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>51.82642681736502</v>
+        <v>51.826426817365</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>22.32152251293537</v>
+        <v>22.32152251293536</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>21.23179796863112</v>
+        <v>21.23179796863111</v>
       </c>
       <c r="W10" s="162" t="n">
         <v>19.03706997814684</v>
@@ -2235,13 +2235,13 @@
         <v>17.10280089232119</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>49.81952878891894</v>
+        <v>49.81952878891892</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>21.29144800593416</v>
+        <v>21.29144800593415</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>19.90738701726304</v>
+        <v>19.90738701726303</v>
       </c>
       <c r="AB10" s="162" t="n">
         <v>17.90121077024454</v>
@@ -2250,19 +2250,19 @@
         <v>16.17008990766154</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>52382.058043266</v>
+        <v>52382.05804326598</v>
       </c>
       <c r="AE10" s="165" t="n">
         <v>44957.25837037079</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>49542.86344087819</v>
+        <v>49542.86344087817</v>
       </c>
       <c r="AG10" s="165" t="n">
         <v>52178.93781677113</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>55418.07027748255</v>
+        <v>55418.07027748253</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2327,7 +2327,7 @@
         <v>289.4760924307366</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>320.5116541187624</v>
+        <v>320.5116541187623</v>
       </c>
       <c r="G11" s="157" t="n">
         <v>316.8750272103919</v>
@@ -2342,7 +2342,7 @@
         <v>234.2963343895348</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>250.2270693893988</v>
+        <v>250.2270693893987</v>
       </c>
       <c r="L11" s="157" t="n">
         <v>243.162109703778</v>
@@ -2357,7 +2357,7 @@
         <v>53353.20043519454</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>63664.61716388015</v>
+        <v>63664.61716388013</v>
       </c>
       <c r="Q11" s="160" t="n">
         <v>69612.19423396252</v>
@@ -2377,7 +2377,7 @@
         <v>343.170077243958</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>379.9623249641656</v>
+        <v>379.9623249641655</v>
       </c>
       <c r="X11" s="157" t="n">
         <v>375.6511518839515</v>
@@ -2392,7 +2392,7 @@
         <v>268.2698850830515</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>285.0465671319957</v>
+        <v>285.0465671319956</v>
       </c>
       <c r="AC11" s="157" t="n">
         <v>276.3416581375951</v>
@@ -2407,7 +2407,7 @@
         <v>53353.20043519454</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>63664.61716388015</v>
+        <v>63664.61716388013</v>
       </c>
       <c r="AH11" s="160" t="n">
         <v>69612.19423396252</v>
@@ -2464,13 +2464,13 @@
         <v>78.74397133151599</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>39.36900667916362</v>
+        <v>39.36900667916361</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>39.26213760819459</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>37.84291271620291</v>
+        <v>37.8429127162029</v>
       </c>
       <c r="G12" s="163" t="n">
         <v>34.68892655150317</v>
@@ -2479,10 +2479,10 @@
         <v>75.1402144932151</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>37.31452726130321</v>
+        <v>37.3145272613032</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>36.49583093868577</v>
+        <v>36.49583093868576</v>
       </c>
       <c r="K12" s="162" t="n">
         <v>35.20142114117247</v>
@@ -2494,7 +2494,7 @@
         <v>93515.7414689015</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>89690.38444825195</v>
+        <v>89690.38444825193</v>
       </c>
       <c r="O12" s="165" t="n">
         <v>102896.0638760727</v>
@@ -2514,7 +2514,7 @@
         <v>83.13197116729431</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>41.4722231171863</v>
+        <v>41.47222311718629</v>
       </c>
       <c r="V12" s="162" t="n">
         <v>41.34199722459471</v>
@@ -2532,10 +2532,10 @@
         <v>39.19870494964348</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>38.28625009656045</v>
+        <v>38.28625009656044</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>36.91430186725892</v>
+        <v>36.91430186725891</v>
       </c>
       <c r="AC12" s="163" t="n">
         <v>33.98390413088459</v>
@@ -2544,7 +2544,7 @@
         <v>93515.7414689015</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>89690.38444825195</v>
+        <v>89690.38444825193</v>
       </c>
       <c r="AF12" s="165" t="n">
         <v>102896.0638760727</v>
@@ -2603,10 +2603,10 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>85.31427063764373</v>
+        <v>85.31427063764372</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>106.4336657728856</v>
+        <v>106.4336657728855</v>
       </c>
       <c r="E13" s="156" t="n">
         <v>116.6269781502456</v>
@@ -2618,10 +2618,10 @@
         <v>131.1011686181122</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>85.31427063764373</v>
+        <v>85.31427063764372</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>106.4336657728856</v>
+        <v>106.4336657728855</v>
       </c>
       <c r="J13" s="156" t="n">
         <v>116.6269781502456</v>
@@ -2636,13 +2636,13 @@
         <v>736.4368637819756</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>805.1896113223746</v>
+        <v>805.1896113223744</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>898.5758174492479</v>
+        <v>898.5758174492477</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>975.4712887117287</v>
+        <v>975.4712887117284</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>1066.629990298585</v>
@@ -2659,13 +2659,13 @@
         <v>30.31338582139146</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>33.21654440988008</v>
+        <v>33.21654440988007</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>35.15261751468424</v>
+        <v>35.15261751468423</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>37.33894042920919</v>
+        <v>37.33894042920917</v>
       </c>
       <c r="Y13" s="155" t="n">
         <v>24.29836821958207</v>
@@ -2674,25 +2674,25 @@
         <v>30.31338582139146</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>33.21654440988008</v>
+        <v>33.21654440988007</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>35.15261751468424</v>
+        <v>35.15261751468423</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>37.33894042920919</v>
+        <v>37.33894042920917</v>
       </c>
       <c r="AD13" s="158" t="n">
         <v>736.4368637819756</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>805.1896113223746</v>
+        <v>805.1896113223744</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>898.5758174492479</v>
+        <v>898.5758174492477</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>975.4712887117287</v>
+        <v>975.4712887117284</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>1066.629990298585</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>78.79138311795597</v>
+        <v>78.79138311795596</v>
       </c>
       <c r="D14" s="168" t="n">
         <v>39.59097023290599</v>
@@ -2758,10 +2758,10 @@
         <v>38.06330008066629</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>34.90606458836059</v>
+        <v>34.90606458836058</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>75.21029445561354</v>
+        <v>75.21029445561352</v>
       </c>
       <c r="I14" s="168" t="n">
         <v>37.53138991504643</v>
@@ -2770,13 +2770,13 @@
         <v>36.71421269678084</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>35.41279060193204</v>
+        <v>35.41279060193203</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>32.61719815176763</v>
+        <v>32.61719815176762</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>94252.17833268348</v>
+        <v>94252.17833268346</v>
       </c>
       <c r="N14" s="171" t="n">
         <v>90495.57405957433</v>
@@ -2788,7 +2788,7 @@
         <v>116819.026269363</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>126096.8945017437</v>
+        <v>126096.8945017436</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>81.58842016735795</v>
+        <v>81.58842016735792</v>
       </c>
       <c r="U14" s="168" t="n">
         <v>41.33683127297982</v>
@@ -2808,10 +2808,10 @@
         <v>39.78555736836314</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>36.50571099967004</v>
+        <v>36.50571099967002</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>77.75475194982047</v>
+        <v>77.75475194982045</v>
       </c>
       <c r="Z14" s="168" t="n">
         <v>39.09674022381645</v>
@@ -2823,10 +2823,10 @@
         <v>36.89886055189965</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>34.00975339094192</v>
+        <v>34.00975339094191</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>94252.17833268348</v>
+        <v>94252.17833268346</v>
       </c>
       <c r="AE14" s="171" t="n">
         <v>90495.57405957433</v>
@@ -2838,7 +2838,7 @@
         <v>116819.026269363</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>126096.8945017437</v>
+        <v>126096.8945017436</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>7.704699476065055</v>
       </c>
       <c r="F24" s="80" t="n">
-        <v>7.903368820239653</v>
+        <v>7.903368820239654</v>
       </c>
       <c r="G24" s="81" t="n">
         <v>8.135930453874115</v>
@@ -3879,7 +3879,7 @@
         <v>7.704699476065055</v>
       </c>
       <c r="P24" s="80" t="n">
-        <v>7.903368820239653</v>
+        <v>7.903368820239654</v>
       </c>
       <c r="Q24" s="81" t="n">
         <v>8.135930453874115</v>
@@ -4408,49 +4408,49 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>29.06346128541953</v>
+        <v>29.06346128541952</v>
       </c>
       <c r="D35" s="149" t="n">
         <v>12.93325813107621</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>11.75360713701505</v>
+        <v>11.75360713701504</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>9.716298370749909</v>
+        <v>9.716298370749907</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>8.273045295813482</v>
+        <v>8.273045295813478</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>28.62013109797843</v>
+        <v>28.62013109797842</v>
       </c>
       <c r="I35" s="149" t="n">
         <v>12.61536042613422</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>11.31085694480148</v>
+        <v>11.31085694480147</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>9.362594739250378</v>
+        <v>9.362594739250376</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>7.99824980305196</v>
+        <v>7.998249803051956</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>26198.60817143321</v>
+        <v>26198.6081714332</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>24909.12870060275</v>
+        <v>24909.12870060274</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>26539.93282039779</v>
+        <v>26539.93282039778</v>
       </c>
       <c r="P35" s="152" t="n">
         <v>25920.71737475279</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>26207.86114920854</v>
+        <v>26207.86114920852</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>30.44053301714764</v>
+        <v>30.44053301714762</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>13.54605589788531</v>
+        <v>13.5460558978853</v>
       </c>
       <c r="V35" s="149" t="n">
         <v>12.31051121582623</v>
@@ -4470,10 +4470,10 @@
         <v>10.17667161026175</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>8.665034973171226</v>
+        <v>8.665034973171222</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>29.95454745609083</v>
+        <v>29.95454745609082</v>
       </c>
       <c r="Z35" s="149" t="n">
         <v>13.19772521659784</v>
@@ -4482,25 +4482,25 @@
         <v>11.82567601561114</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>9.789323971681085</v>
+        <v>9.789323971681084</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>8.364055776196878</v>
+        <v>8.364055776196874</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>26198.60817143321</v>
+        <v>26198.6081714332</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>24909.12870060275</v>
+        <v>24909.12870060274</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>26539.93282039779</v>
+        <v>26539.93282039778</v>
       </c>
       <c r="AG35" s="152" t="n">
         <v>25920.71737475279</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>26207.86114920854</v>
+        <v>26207.86114920852</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4519,7 +4519,7 @@
         <v>143.2977451395557</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>152.3124872651065</v>
+        <v>152.3124872651066</v>
       </c>
       <c r="G36" s="157" t="n">
         <v>152.1157564838712</v>
@@ -4569,7 +4569,7 @@
         <v>143.9914100520051</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>153.0497900610494</v>
+        <v>153.0497900610495</v>
       </c>
       <c r="X36" s="157" t="n">
         <v>152.8521069602922</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>46.04048623845073</v>
+        <v>46.04048623845072</v>
       </c>
       <c r="D37" s="162" t="n">
         <v>22.33265031143399</v>
@@ -4624,13 +4624,13 @@
         <v>19.41911503247201</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>17.486022938494</v>
+        <v>17.48602293849399</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>44.32534480636672</v>
+        <v>44.3253448063667</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>21.34328391278312</v>
+        <v>21.34328391278311</v>
       </c>
       <c r="J37" s="162" t="n">
         <v>20.10509087017041</v>
@@ -4642,19 +4642,19 @@
         <v>16.57095507174424</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>48445.0119104881</v>
+        <v>48445.01191048809</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>46944.40040916394</v>
+        <v>46944.40040916392</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>52105.87191382804</v>
+        <v>52105.87191382803</v>
       </c>
       <c r="P37" s="165" t="n">
         <v>55587.89197278408</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>59183.97012037395</v>
+        <v>59183.97012037394</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>47.931142040496</v>
+        <v>47.93114204049598</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>23.30814930832186</v>
+        <v>23.30814930832185</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>22.33018579505337</v>
@@ -4677,13 +4677,13 @@
         <v>18.26501088756105</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>46.07508287590759</v>
+        <v>46.07508287590758</v>
       </c>
       <c r="Z37" s="162" t="n">
         <v>22.23254479281594</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>20.93725889094723</v>
+        <v>20.93725889094722</v>
       </c>
       <c r="AB37" s="162" t="n">
         <v>19.07073260043547</v>
@@ -4692,19 +4692,19 @@
         <v>17.26891811907159</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>48445.0119104881</v>
+        <v>48445.01191048809</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>46944.40040916394</v>
+        <v>46944.40040916392</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>52105.87191382804</v>
+        <v>52105.87191382803</v>
       </c>
       <c r="AG37" s="165" t="n">
         <v>55587.89197278408</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>59183.97012037395</v>
+        <v>59183.97012037394</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4723,7 +4723,7 @@
         <v>304.7626318059581</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>341.7608589849468</v>
+        <v>341.7608589849467</v>
       </c>
       <c r="G38" s="157" t="n">
         <v>338.7294552555375</v>
@@ -4753,7 +4753,7 @@
         <v>56170.65521150504</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>67885.43870174914</v>
+        <v>67885.43870174912</v>
       </c>
       <c r="Q38" s="160" t="n">
         <v>74413.25004244293</v>
@@ -4773,7 +4773,7 @@
         <v>361.2920674025847</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>405.1529761646477</v>
+        <v>405.1529761646476</v>
       </c>
       <c r="X38" s="157" t="n">
         <v>401.5592871548103</v>
@@ -4788,7 +4788,7 @@
         <v>282.436575420318</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>303.9445161567947</v>
+        <v>303.9445161567946</v>
       </c>
       <c r="AC38" s="157" t="n">
         <v>295.4005563310286</v>
@@ -4803,7 +4803,7 @@
         <v>56170.65521150504</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>67885.43870174914</v>
+        <v>67885.43870174912</v>
       </c>
       <c r="AH38" s="160" t="n">
         <v>74413.25004244293</v>
@@ -4819,10 +4819,10 @@
         <v>75.86677992454086</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>41.1400915223824</v>
+        <v>41.14009152238239</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>41.3151654941079</v>
+        <v>41.31516549410789</v>
       </c>
       <c r="F39" s="162" t="n">
         <v>40.33535120944499</v>
@@ -4837,10 +4837,10 @@
         <v>38.99318769088791</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>38.40420789422528</v>
+        <v>38.40420789422527</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>37.51988372165767</v>
+        <v>37.51988372165766</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>34.63016969172003</v>
@@ -4849,7 +4849,7 @@
         <v>90098.81083635232</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>93725.26604364756</v>
+        <v>93725.26604364754</v>
       </c>
       <c r="O39" s="165" t="n">
         <v>108276.5271253331</v>
@@ -4869,13 +4869,13 @@
         <v>80.09444856025617</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>43.33792489564419</v>
+        <v>43.33792489564418</v>
       </c>
       <c r="V39" s="162" t="n">
         <v>43.50378153721778</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>42.45305785656496</v>
+        <v>42.45305785656495</v>
       </c>
       <c r="X39" s="163" t="n">
         <v>38.99962343783456</v>
@@ -4884,13 +4884,13 @@
         <v>76.23446740928134</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>40.96212846641871</v>
+        <v>40.9621284664187</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>40.28824855827651</v>
+        <v>40.2882485582765</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>39.34557949155555</v>
+        <v>39.34557949155553</v>
       </c>
       <c r="AC39" s="163" t="n">
         <v>36.31244914906384</v>
@@ -4899,7 +4899,7 @@
         <v>90098.81083635232</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>93725.26604364756</v>
+        <v>93725.26604364754</v>
       </c>
       <c r="AF39" s="165" t="n">
         <v>108276.5271253331</v>
@@ -4924,10 +4924,10 @@
         <v>101.9262551993843</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>112.8247865600319</v>
+        <v>112.8247865600318</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>121.1482847990558</v>
+        <v>121.1482847990557</v>
       </c>
       <c r="G40" s="157" t="n">
         <v>129.3107001526823</v>
@@ -4939,10 +4939,10 @@
         <v>101.9262551993843</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>112.8247865600319</v>
+        <v>112.8247865600318</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>121.1482847990558</v>
+        <v>121.1482847990557</v>
       </c>
       <c r="L40" s="157" t="n">
         <v>129.3107001526823</v>
@@ -4951,13 +4951,13 @@
         <v>687.6601186702486</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687164</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>869.281073896229</v>
+        <v>869.2810738962288</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063708</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>1052.062863383992</v>
@@ -4974,13 +4974,13 @@
         <v>29.02962964539426</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>32.13364174178123</v>
+        <v>32.13364174178122</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>34.504258328845</v>
+        <v>34.50425832884499</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>36.82899687892851</v>
+        <v>36.8289968789285</v>
       </c>
       <c r="Y40" s="155" t="n">
         <v>22.68900376274206</v>
@@ -4989,25 +4989,25 @@
         <v>29.02962964539426</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>32.13364174178123</v>
+        <v>32.13364174178122</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>34.504258328845</v>
+        <v>34.50425832884499</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>36.82899687892851</v>
+        <v>36.8289968789285</v>
       </c>
       <c r="AD40" s="158" t="n">
         <v>687.6601186702486</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687164</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>869.281073896229</v>
+        <v>869.2810738962288</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063708</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>1052.062863383992</v>
@@ -5023,13 +5023,13 @@
         <v>75.89417816631915</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>41.34127517246637</v>
+        <v>41.34127517246636</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>41.52477957589833</v>
+        <v>41.52477957589832</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>40.54345786920423</v>
+        <v>40.54345786920421</v>
       </c>
       <c r="G41" s="181" t="n">
         <v>37.27353150655126</v>
@@ -5038,13 +5038,13 @@
         <v>72.44476821545784</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>39.19064142543941</v>
+        <v>39.1906414254394</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>38.60702661544716</v>
+        <v>38.60702661544715</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>37.72024445483262</v>
+        <v>37.72024445483261</v>
       </c>
       <c r="L41" s="181" t="n">
         <v>34.82942512433012</v>
@@ -5053,7 +5053,7 @@
         <v>90786.47095502257</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>94496.35629231627</v>
+        <v>94496.35629231625</v>
       </c>
       <c r="O41" s="183" t="n">
         <v>109145.8081992293</v>
@@ -5079,7 +5079,7 @@
         <v>43.38152731751639</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>42.37793532217563</v>
+        <v>42.37793532217562</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>38.9816722441114</v>
@@ -5088,10 +5088,10 @@
         <v>74.89566452873704</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>40.82519540265868</v>
+        <v>40.82519540265867</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>40.20698464244926</v>
+        <v>40.20698464244925</v>
       </c>
       <c r="AB41" s="186" t="n">
         <v>39.30314489382545</v>
@@ -5103,7 +5103,7 @@
         <v>90786.47095502257</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>94496.35629231627</v>
+        <v>94496.35629231625</v>
       </c>
       <c r="AF41" s="189" t="n">
         <v>109145.8081992293</v>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="C46" s="148" t="n">
-        <v>4.799645254128302</v>
+        <v>4.799645254128301</v>
       </c>
       <c r="D46" s="149" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="148" t="n">
-        <v>4.726432101391021</v>
+        <v>4.72643210139102</v>
       </c>
       <c r="I46" s="149" t="n">
         <v>0</v>
@@ -5401,7 +5401,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="151" t="n">
-        <v>4326.533035412036</v>
+        <v>4326.533035412035</v>
       </c>
       <c r="N46" s="152" t="n">
         <v>0</v>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="T46" s="148" t="n">
-        <v>5.0270598671668</v>
+        <v>5.027059867166798</v>
       </c>
       <c r="U46" s="149" t="n">
         <v>0</v>
@@ -5436,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="Y46" s="148" t="n">
-        <v>4.946802451548126</v>
+        <v>4.946802451548124</v>
       </c>
       <c r="Z46" s="149" t="n">
         <v>0</v>
@@ -5451,7 +5451,7 @@
         <v>0</v>
       </c>
       <c r="AD46" s="151" t="n">
-        <v>4326.533035412036</v>
+        <v>4326.533035412035</v>
       </c>
       <c r="AE46" s="152" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="C47" s="155" t="n">
-        <v>3.383657686580601</v>
+        <v>3.3836576865806</v>
       </c>
       <c r="D47" s="156" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="H47" s="155" t="n">
-        <v>2.873833781895742</v>
+        <v>2.873833781895741</v>
       </c>
       <c r="I47" s="156" t="n">
         <v>0</v>
@@ -5503,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="158" t="n">
-        <v>510.2510503017754</v>
+        <v>510.2510503017753</v>
       </c>
       <c r="N47" s="159" t="n">
         <v>0</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="T47" s="155" t="n">
-        <v>3.400037041403211</v>
+        <v>3.40003704140321</v>
       </c>
       <c r="U47" s="156" t="n">
         <v>0</v>
@@ -5538,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="Y47" s="155" t="n">
-        <v>2.885640538168157</v>
+        <v>2.885640538168156</v>
       </c>
       <c r="Z47" s="156" t="n">
         <v>0</v>
@@ -5553,7 +5553,7 @@
         <v>0</v>
       </c>
       <c r="AD47" s="158" t="n">
-        <v>510.2510503017754</v>
+        <v>510.2510503017753</v>
       </c>
       <c r="AE47" s="159" t="n">
         <v>0</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="C48" s="161" t="n">
-        <v>4.596714550264223</v>
+        <v>4.596714550264222</v>
       </c>
       <c r="D48" s="162" t="n">
         <v>0</v>
@@ -5590,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="161" t="n">
-        <v>4.425473622534027</v>
+        <v>4.425473622534026</v>
       </c>
       <c r="I48" s="162" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="164" t="n">
-        <v>4836.784085713812</v>
+        <v>4836.784085713811</v>
       </c>
       <c r="N48" s="165" t="n">
         <v>0</v>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="T48" s="161" t="n">
-        <v>4.785478956221883</v>
+        <v>4.785478956221882</v>
       </c>
       <c r="U48" s="162" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="Y48" s="161" t="n">
-        <v>4.600168702897723</v>
+        <v>4.600168702897722</v>
       </c>
       <c r="Z48" s="162" t="n">
         <v>0</v>
@@ -5655,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="AD48" s="164" t="n">
-        <v>4836.784085713812</v>
+        <v>4836.784085713811</v>
       </c>
       <c r="AE48" s="165" t="n">
         <v>0</v>
@@ -5794,7 +5794,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="161" t="n">
-        <v>4.198069564927029</v>
+        <v>4.198069564927028</v>
       </c>
       <c r="I50" s="162" t="n">
         <v>0</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="T50" s="161" t="n">
-        <v>4.644567498024943</v>
+        <v>4.644567498024942</v>
       </c>
       <c r="U50" s="162" t="n">
         <v>0</v>
@@ -5844,7 +5844,7 @@
         <v>0</v>
       </c>
       <c r="Y50" s="161" t="n">
-        <v>4.420732471764425</v>
+        <v>4.420732471764424</v>
       </c>
       <c r="Z50" s="162" t="n">
         <v>0</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="T52" s="185" t="n">
-        <v>4.522713209885903</v>
+        <v>4.522713209885902</v>
       </c>
       <c r="U52" s="186" t="n">
         <v>0</v>
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="Y52" s="185" t="n">
-        <v>4.31020043106005</v>
+        <v>4.310200431060049</v>
       </c>
       <c r="Z52" s="186" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>9.772854192859578</v>
+        <v>9.772854192859574</v>
       </c>
       <c r="N57" s="152" t="n">
         <v>0</v>
@@ -6414,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>9.772854192859578</v>
+        <v>9.772854192859574</v>
       </c>
       <c r="AE57" s="152" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>0.3712528407756716</v>
+        <v>0.3712528407756715</v>
       </c>
       <c r="D58" s="156" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>0.3153152754420838</v>
+        <v>0.3153152754420837</v>
       </c>
       <c r="I58" s="156" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>55.984431488026</v>
+        <v>55.98443148802599</v>
       </c>
       <c r="N58" s="159" t="n">
         <v>0</v>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>0.3730499735152165</v>
+        <v>0.3730499735152164</v>
       </c>
       <c r="U58" s="156" t="n">
         <v>0</v>
@@ -6501,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>0.3166107054803716</v>
+        <v>0.3166107054803715</v>
       </c>
       <c r="Z58" s="156" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>55.984431488026</v>
+        <v>55.98443148802599</v>
       </c>
       <c r="AE58" s="159" t="n">
         <v>0</v>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.062493480485929</v>
+        <v>0.06249348048592897</v>
       </c>
       <c r="D59" s="162" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.06016541737509602</v>
+        <v>0.06016541737509599</v>
       </c>
       <c r="I59" s="162" t="n">
         <v>0</v>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="N59" s="165" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.06505977965268386</v>
+        <v>0.06505977965268384</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0</v>
@@ -6603,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.06254044055226261</v>
+        <v>0.06254044055226259</v>
       </c>
       <c r="Z59" s="162" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="AE59" s="165" t="n">
         <v>0</v>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.05537024822944802</v>
+        <v>0.05537024822944799</v>
       </c>
       <c r="D61" s="162" t="n">
         <v>0</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.05283620140248251</v>
+        <v>0.05283620140248248</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0</v>
@@ -6772,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="N61" s="165" t="n">
         <v>0</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.05845574971012556</v>
+        <v>0.05845574971012554</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.05563859950679485</v>
+        <v>0.05563859950679483</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="AE61" s="165" t="n">
         <v>0</v>
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.05497069224853027</v>
+        <v>0.05497069224853025</v>
       </c>
       <c r="D63" s="180" t="n">
         <v>0</v>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.05247226012331142</v>
+        <v>0.0524722601233114</v>
       </c>
       <c r="I63" s="180" t="n">
         <v>0</v>
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="N63" s="183" t="n">
         <v>0</v>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.05692211202015976</v>
+        <v>0.05692211202015974</v>
       </c>
       <c r="U63" s="186" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.0542474617293566</v>
+        <v>0.05424746172935657</v>
       </c>
       <c r="Z63" s="186" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="AE63" s="189" t="n">
         <v>0</v>
@@ -7297,40 +7297,40 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.147141945442066</v>
+        <v>0.1471419454420659</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.03663247190347482</v>
+        <v>0.03663247190347481</v>
       </c>
       <c r="E68" s="149" t="n">
         <v>0.01431807736221277</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.005411602615854709</v>
+        <v>0.005411602615854708</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.005002985281895764</v>
+        <v>0.005002985281895763</v>
       </c>
       <c r="H68" s="148" t="n">
         <v>0.1448974617030969</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.03573205078557531</v>
+        <v>0.03573205078557529</v>
       </c>
       <c r="J68" s="149" t="n">
         <v>0.01377872536326052</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.005214603365273601</v>
+        <v>0.0052146033652736</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.004836807320013591</v>
+        <v>0.004836807320013589</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>132.6378209519391</v>
+        <v>132.637820951939</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>70.55321621334858</v>
+        <v>70.55321621334855</v>
       </c>
       <c r="O68" s="152" t="n">
         <v>32.33056940568208</v>
@@ -7350,37 +7350,37 @@
         <v>0.1541137583183733</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.03836817506099607</v>
+        <v>0.03836817506099605</v>
       </c>
       <c r="V68" s="149" t="n">
         <v>0.01499649000531013</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.005668012714860293</v>
+        <v>0.005668012714860292</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.005240034459840949</v>
+        <v>0.005240034459840947</v>
       </c>
       <c r="Y68" s="148" t="n">
         <v>0.151653319755726</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.03738155484773976</v>
+        <v>0.03738155484773974</v>
       </c>
       <c r="AA68" s="149" t="n">
         <v>0.01440587064704166</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.005452275052820333</v>
+        <v>0.005452275052820332</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.005058022342322208</v>
+        <v>0.005058022342322206</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>132.6378209519391</v>
+        <v>132.637820951939</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>70.55321621334858</v>
+        <v>70.55321621334855</v>
       </c>
       <c r="AF68" s="152" t="n">
         <v>32.33056940568208</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>0.845066219028563</v>
+        <v>0.8450662190285628</v>
       </c>
       <c r="D69" s="156" t="n">
         <v>0.3798975964538547</v>
@@ -7408,13 +7408,13 @@
         <v>0.4220668701846503</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>0.4236427786325577</v>
+        <v>0.4236427786325576</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>0.4165487326267491</v>
+        <v>0.416548732626749</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>0.7177380436013975</v>
+        <v>0.7177380436013974</v>
       </c>
       <c r="I69" s="156" t="n">
         <v>0.297315247957744</v>
@@ -7429,7 +7429,7 @@
         <v>0.3062607452808095</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>127.4348547561338</v>
+        <v>127.4348547561337</v>
       </c>
       <c r="N69" s="159" t="n">
         <v>66.89145973609607</v>
@@ -7438,10 +7438,10 @@
         <v>75.30150517013892</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>82.51644042166787</v>
+        <v>82.51644042166785</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>90.30068098406998</v>
+        <v>90.30068098406997</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>0.8491569518189886</v>
+        <v>0.8491569518189884</v>
       </c>
       <c r="U69" s="156" t="n">
         <v>0.3817365760744151</v>
@@ -7461,10 +7461,10 @@
         <v>0.4256935166303105</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>0.4185651303018629</v>
+        <v>0.4185651303018628</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>0.7206867729961266</v>
+        <v>0.7206867729961265</v>
       </c>
       <c r="Z69" s="156" t="n">
         <v>0.2984404264743437</v>
@@ -7479,7 +7479,7 @@
         <v>0.3073493518778007</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>127.4348547561338</v>
+        <v>127.4348547561337</v>
       </c>
       <c r="AE69" s="159" t="n">
         <v>66.89145973609607</v>
@@ -7488,10 +7488,10 @@
         <v>75.30150517013892</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>82.51644042166787</v>
+        <v>82.51644042166785</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>90.30068098406998</v>
+        <v>90.30068098406997</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7504,22 +7504,22 @@
         <v>0.2471641965752578</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.06538594291105519</v>
+        <v>0.06538594291105518</v>
       </c>
       <c r="E70" s="162" t="n">
         <v>0.0441760353993298</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.03386972940431261</v>
+        <v>0.0338697294043126</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.03136206693373803</v>
+        <v>0.03136206693373802</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.2379566145380389</v>
+        <v>0.2379566145380388</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.06248925783525022</v>
+        <v>0.06248925783525021</v>
       </c>
       <c r="J70" s="162" t="n">
         <v>0.04152991899781572</v>
@@ -7540,7 +7540,7 @@
         <v>107.632074575821</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>96.95327805237727</v>
+        <v>96.95327805237726</v>
       </c>
       <c r="Q70" s="166" t="n">
         <v>106.1494451224471</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.2573140116726188</v>
+        <v>0.2573140116726187</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.06824202675380649</v>
+        <v>0.06824202675380647</v>
       </c>
       <c r="V70" s="162" t="n">
         <v>0.04612616840497182</v>
@@ -7563,19 +7563,19 @@
         <v>0.03537263148926338</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.03275922123721514</v>
+        <v>0.03275922123721513</v>
       </c>
       <c r="Y70" s="161" t="n">
         <v>0.2473499255021189</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.06509285213883771</v>
+        <v>0.0650928521388377</v>
       </c>
       <c r="AA70" s="162" t="n">
         <v>0.04324888016633795</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.03326210033972533</v>
+        <v>0.03326210033972532</v>
       </c>
       <c r="AC70" s="163" t="n">
         <v>0.03097267845459029</v>
@@ -7590,7 +7590,7 @@
         <v>107.632074575821</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>96.95327805237727</v>
+        <v>96.95327805237726</v>
       </c>
       <c r="AH70" s="166" t="n">
         <v>106.1494451224471</v>
@@ -7609,7 +7609,7 @@
         <v>0.3756597890879749</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.3190001249957816</v>
+        <v>0.3190001249957817</v>
       </c>
       <c r="F71" s="156" t="n">
         <v>0.2898236696578319</v>
@@ -7624,7 +7624,7 @@
         <v>0.3241456711598434</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.258192513684695</v>
+        <v>0.2581925136846951</v>
       </c>
       <c r="K71" s="156" t="n">
         <v>0.2262686132195627</v>
@@ -7639,7 +7639,7 @@
         <v>66.17075728781755</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>58.79476078607205</v>
+        <v>58.79476078607207</v>
       </c>
       <c r="P71" s="159" t="n">
         <v>57.56892998018633</v>
@@ -7659,7 +7659,7 @@
         <v>0.445339709252898</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>0.3781704271893471</v>
+        <v>0.3781704271893472</v>
       </c>
       <c r="W71" s="156" t="n">
         <v>0.3435821254475554</v>
@@ -7674,7 +7674,7 @@
         <v>0.3747386467801407</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.2956310697560413</v>
+        <v>0.2956310697560414</v>
       </c>
       <c r="AB71" s="156" t="n">
         <v>0.2577542533880874</v>
@@ -7689,7 +7689,7 @@
         <v>66.17075728781755</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>58.79476078607205</v>
+        <v>58.79476078607207</v>
       </c>
       <c r="AG71" s="159" t="n">
         <v>57.56892998018633</v>
@@ -7708,31 +7708,31 @@
         <v>0.2627513253376128</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.08937566050598865</v>
+        <v>0.08937566050598862</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.06350362750070618</v>
+        <v>0.06350362750070619</v>
       </c>
       <c r="F72" s="162" t="n">
         <v>0.05047816801088278</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.04710469312540088</v>
+        <v>0.04710469312540087</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.2507263808314286</v>
+        <v>0.2507263808314285</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.08471157394511497</v>
+        <v>0.08471157394511494</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.05902932938565544</v>
+        <v>0.05902932938565546</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.04695471682931907</v>
+        <v>0.04695471682931906</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.04400942212605256</v>
+        <v>0.04400942212605255</v>
       </c>
       <c r="M72" s="164" t="n">
         <v>312.0414756253109</v>
@@ -7741,7 +7741,7 @@
         <v>203.6154332372622</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>166.426835361893</v>
+        <v>166.4268353618931</v>
       </c>
       <c r="P72" s="165" t="n">
         <v>154.5222080325636</v>
@@ -7758,31 +7758,31 @@
         <v>0.2773931163590231</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.09415039002525837</v>
+        <v>0.09415039002525835</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.06686764786178981</v>
+        <v>0.06686764786178982</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.05312839786449203</v>
+        <v>0.05312839786449202</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.04956230090443734</v>
+        <v>0.04956230090443733</v>
       </c>
       <c r="Y72" s="161" t="n">
         <v>0.2640247466429813</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.08898904090734812</v>
+        <v>0.08898904090734809</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.06192520103702654</v>
+        <v>0.06192520103702655</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.04923950610340088</v>
+        <v>0.04923950610340087</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.04614733099081714</v>
+        <v>0.04614733099081713</v>
       </c>
       <c r="AD72" s="164" t="n">
         <v>312.0414756253109</v>
@@ -7791,7 +7791,7 @@
         <v>203.6154332372622</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>166.426835361893</v>
+        <v>166.4268353618931</v>
       </c>
       <c r="AG72" s="165" t="n">
         <v>154.5222080325636</v>
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>7.825390701591194</v>
+        <v>7.825390701591192</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>9.546277323050761</v>
+        <v>9.546277323050759</v>
       </c>
       <c r="E73" s="156" t="n">
         <v>10.05861667760935</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>10.44461166199181</v>
+        <v>10.4446116619918</v>
       </c>
       <c r="G73" s="157" t="n">
         <v>10.810665665364</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>7.825390701591194</v>
+        <v>7.825390701591192</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>9.546277323050761</v>
+        <v>9.546277323050759</v>
       </c>
       <c r="J73" s="156" t="n">
         <v>10.05861667760935</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>10.44461166199181</v>
+        <v>10.4446116619918</v>
       </c>
       <c r="L73" s="157" t="n">
         <v>10.810665665364</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>67.54914673800951</v>
+        <v>67.5491467380095</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121333</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>82.5476181488975</v>
+        <v>82.54761814889748</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>87.95482401348623</v>
+        <v>87.95482401348622</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>2.228750516275973</v>
+        <v>2.228750516275972</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>2.718876452767622</v>
+        <v>2.718876452767621</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>2.864795889192536</v>
+        <v>2.864795889192535</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>2.974731169554628</v>
+        <v>2.974731169554627</v>
       </c>
       <c r="X73" s="157" t="n">
         <v>3.078987056591012</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>2.228750516275973</v>
+        <v>2.228750516275972</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>2.718876452767622</v>
+        <v>2.718876452767621</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>2.864795889192536</v>
+        <v>2.864795889192535</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>2.974731169554628</v>
+        <v>2.974731169554627</v>
       </c>
       <c r="AC73" s="157" t="n">
         <v>3.078987056591012</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>67.54914673800951</v>
+        <v>67.5491467380095</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121333</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>82.5476181488975</v>
+        <v>82.54761814889748</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>87.95482401348623</v>
+        <v>87.95482401348622</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,40 +7909,40 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.3173239142446481</v>
+        <v>0.317323914244648</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>0.1206751188015574</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.09280201299289764</v>
+        <v>0.09280201299289766</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.07724477957220312</v>
+        <v>0.0772447795722031</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.07134620487753214</v>
+        <v>0.07134620487753213</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.3029014605876229</v>
+        <v>0.3029014605876228</v>
       </c>
       <c r="I74" s="180" t="n">
         <v>0.1143974221935446</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.08628124753884052</v>
+        <v>0.08628124753884053</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.07186589702641839</v>
+        <v>0.07186589702641838</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.06666787933014513</v>
+        <v>0.06666787933014512</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>379.5906223633204</v>
+        <v>379.5906223633203</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>275.8347190384756</v>
+        <v>275.8347190384755</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>243.925454007809</v>
@@ -7959,40 +7959,40 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.3285886834323496</v>
+        <v>0.3285886834323495</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.1259965844585626</v>
+        <v>0.1259965844585625</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.09695158175164874</v>
+        <v>0.09695158175164875</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.08073988862141393</v>
+        <v>0.08073988862141392</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.07461580005930891</v>
+        <v>0.0746158000593089</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.3131489924843802</v>
+        <v>0.3131489924843801</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.119168682745272</v>
+        <v>0.1191686827452719</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.08985692758160994</v>
+        <v>0.08985692758160996</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.0748816929629465</v>
+        <v>0.07488169296294649</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.06951419078258367</v>
+        <v>0.06951419078258364</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>379.5906223633204</v>
+        <v>379.5906223633203</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>275.8347190384756</v>
+        <v>275.8347190384755</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>243.925454007809</v>
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>34.02109001396059</v>
+        <v>34.02109001396057</v>
       </c>
       <c r="D79" s="149" t="n">
         <v>12.96989060297969</v>
@@ -8269,40 +8269,40 @@
         <v>11.76792521437726</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>9.721709973365764</v>
+        <v>9.721709973365762</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>8.278048281095378</v>
+        <v>8.278048281095375</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>33.50213681479686</v>
+        <v>33.50213681479683</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>12.6510924769198</v>
+        <v>12.65109247691979</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>11.32463567016474</v>
+        <v>11.32463567016473</v>
       </c>
       <c r="K79" s="149" t="n">
         <v>9.367809342615651</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>8.003086610371973</v>
+        <v>8.00308661037197</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>30667.55188199005</v>
+        <v>30667.55188199003</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>24979.6819168161</v>
+        <v>24979.68191681609</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>26572.26338980347</v>
+        <v>26572.26338980346</v>
       </c>
       <c r="P79" s="152" t="n">
         <v>25935.1542123835</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>26223.70991334691</v>
+        <v>26223.7099133469</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>35.63306186000859</v>
+        <v>35.63306186000857</v>
       </c>
       <c r="U79" s="149" t="n">
         <v>13.5844240729463</v>
@@ -8322,37 +8322,37 @@
         <v>10.18233962297661</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>8.670275007631068</v>
+        <v>8.670275007631062</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>35.0641771578106</v>
+        <v>35.06417715781058</v>
       </c>
       <c r="Z79" s="149" t="n">
         <v>13.23510677144558</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>11.84008188625819</v>
+        <v>11.84008188625818</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>9.794776246733907</v>
+        <v>9.794776246733905</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>8.369113798539201</v>
+        <v>8.369113798539196</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>30667.55188199005</v>
+        <v>30667.55188199003</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>24979.6819168161</v>
+        <v>24979.68191681609</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>26572.26338980347</v>
+        <v>26572.26338980346</v>
       </c>
       <c r="AG79" s="152" t="n">
         <v>25935.1542123835</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>26223.70991334691</v>
+        <v>26223.7099133469</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>152.1238573261689</v>
+        <v>152.1238573261688</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>125.5251222980276</v>
@@ -8386,13 +8386,13 @@
         <v>104.5457635012763</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>111.043636242772</v>
+        <v>111.0436362427721</v>
       </c>
       <c r="L80" s="157" t="n">
         <v>112.1469201944818</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>22940.07407560083</v>
+        <v>22940.07407560082</v>
       </c>
       <c r="N80" s="159" t="n">
         <v>22102.16316829728</v>
@@ -8401,7 +8401,7 @@
         <v>25641.24059860039</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>29749.69103845296</v>
+        <v>29749.69103845297</v>
       </c>
       <c r="Q80" s="160" t="n">
         <v>33066.40965214949</v>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>152.8602470165361</v>
+        <v>152.860247016536</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>126.1327548388207</v>
@@ -8421,7 +8421,7 @@
         <v>144.4155200316488</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>153.4754835776797</v>
+        <v>153.4754835776798</v>
       </c>
       <c r="X80" s="157" t="n">
         <v>153.270672090594</v>
@@ -8436,13 +8436,13 @@
         <v>104.913412981438</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>111.433921772961</v>
+        <v>111.4339217729611</v>
       </c>
       <c r="AC80" s="157" t="n">
         <v>112.5455474395243</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>22940.07407560083</v>
+        <v>22940.07407560082</v>
       </c>
       <c r="AE80" s="159" t="n">
         <v>22102.16316829728</v>
@@ -8451,7 +8451,7 @@
         <v>25641.24059860039</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>29749.69103845296</v>
+        <v>29749.69103845297</v>
       </c>
       <c r="AH80" s="160" t="n">
         <v>33066.40965214949</v>
@@ -8464,28 +8464,28 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>50.94685846577615</v>
+        <v>50.94685846577612</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>22.39803625434505</v>
+        <v>22.39803625434504</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>21.43028097902091</v>
+        <v>21.4302809790209</v>
       </c>
       <c r="F81" s="162" t="n">
         <v>19.45298476187632</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>17.51738500542774</v>
+        <v>17.51738500542773</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>49.04894046081388</v>
+        <v>49.04894046081385</v>
       </c>
       <c r="I81" s="162" t="n">
         <v>21.40577317061837</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>20.14662078916823</v>
+        <v>20.14662078916822</v>
       </c>
       <c r="K81" s="162" t="n">
         <v>18.33879962767348</v>
@@ -8494,19 +8494,19 @@
         <v>16.60067591815649</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>53607.62595759088</v>
+        <v>53607.62595759085</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>47081.84508511338</v>
+        <v>47081.84508511337</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>52213.50398840386</v>
+        <v>52213.50398840385</v>
       </c>
       <c r="P81" s="165" t="n">
         <v>55684.84525083646</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>59290.11956549641</v>
+        <v>59290.1195654964</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>53.03899478804319</v>
+        <v>53.03899478804316</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>23.37639133507566</v>
+        <v>23.37639133507565</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>22.37631196345835</v>
+        <v>22.37631196345834</v>
       </c>
       <c r="W81" s="162" t="n">
         <v>20.31617238903868</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>18.29777010879828</v>
+        <v>18.29777010879827</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>50.98514194485971</v>
+        <v>50.98514194485968</v>
       </c>
       <c r="Z81" s="162" t="n">
         <v>22.29763764495478</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>20.98050777111357</v>
+        <v>20.98050777111356</v>
       </c>
       <c r="AB81" s="162" t="n">
         <v>19.1039947007752</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>17.29989079752619</v>
+        <v>17.29989079752618</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>53607.62595759088</v>
+        <v>53607.62595759085</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>47081.84508511338</v>
+        <v>47081.84508511337</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>52213.50398840386</v>
+        <v>52213.50398840385</v>
       </c>
       <c r="AG81" s="165" t="n">
         <v>55684.84525083646</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>59290.11956549641</v>
+        <v>59290.1195654964</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8575,7 +8575,7 @@
         <v>305.0816319309538</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>342.0506826546046</v>
+        <v>342.0506826546045</v>
       </c>
       <c r="G82" s="157" t="n">
         <v>339.0191052830177</v>
@@ -8605,7 +8605,7 @@
         <v>56229.44997229111</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>67943.00763172933</v>
+        <v>67943.00763172931</v>
       </c>
       <c r="Q82" s="160" t="n">
         <v>74476.88135523627</v>
@@ -8640,7 +8640,7 @@
         <v>282.7322064900741</v>
       </c>
       <c r="AB82" s="156" t="n">
-        <v>304.2022704101828</v>
+        <v>304.2022704101827</v>
       </c>
       <c r="AC82" s="157" t="n">
         <v>295.6531555010488</v>
@@ -8655,7 +8655,7 @@
         <v>56229.44997229111</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>67943.00763172933</v>
+        <v>67943.00763172931</v>
       </c>
       <c r="AH82" s="160" t="n">
         <v>74476.88135523627</v>
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>80.58431227565067</v>
+        <v>80.58431227565066</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>41.22946718288838</v>
@@ -8683,22 +8683,22 @@
         <v>37.11288373327718</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>76.89633132279111</v>
+        <v>76.8963313227911</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>39.07789926483303</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>38.46323722361093</v>
+        <v>38.46323722361092</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>37.56683843848699</v>
+        <v>37.56683843848698</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>34.67417911384609</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>95701.31637750981</v>
+        <v>95701.31637750979</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>93928.88147688481</v>
@@ -8718,16 +8718,16 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>85.07486492435028</v>
+        <v>85.07486492435027</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>43.43207528566944</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>43.57064918507957</v>
+        <v>43.57064918507956</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>42.50618625442945</v>
+        <v>42.50618625442944</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>39.04918573873901</v>
@@ -8739,7 +8739,7 @@
         <v>41.05111750732605</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>40.35017375931353</v>
+        <v>40.35017375931352</v>
       </c>
       <c r="AB83" s="162" t="n">
         <v>39.39481899765894</v>
@@ -8748,7 +8748,7 @@
         <v>36.35859648005466</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>95701.31637750981</v>
+        <v>95701.31637750979</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>93928.88147688481</v>
@@ -8773,7 +8773,7 @@
         <v>87.48900391299664</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>111.4725325224351</v>
+        <v>111.472532522435</v>
       </c>
       <c r="E84" s="156" t="n">
         <v>122.8834032376412</v>
@@ -8788,7 +8788,7 @@
         <v>87.48900391299665</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>111.4725325224351</v>
+        <v>111.472532522435</v>
       </c>
       <c r="J84" s="156" t="n">
         <v>122.8834032376412</v>
@@ -8803,13 +8803,13 @@
         <v>755.2092654082581</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699298</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>946.779692542145</v>
+        <v>946.7796925421447</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="Q84" s="160" t="n">
         <v>1140.017687397478</v>
@@ -8823,43 +8823,43 @@
         <v>24.91775427901804</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>31.74850609816189</v>
+        <v>31.74850609816188</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>34.99843763097376</v>
+        <v>34.99843763097375</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>37.47898949839963</v>
+        <v>37.47898949839962</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>39.90798393551952</v>
+        <v>39.90798393551951</v>
       </c>
       <c r="Y84" s="155" t="n">
         <v>24.91775427901804</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>31.74850609816189</v>
+        <v>31.74850609816188</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>34.99843763097376</v>
+        <v>34.99843763097375</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>37.47898949839963</v>
+        <v>37.47898949839962</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>39.90798393551952</v>
+        <v>39.90798393551951</v>
       </c>
       <c r="AD84" s="158" t="n">
         <v>755.2092654082581</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699298</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>946.779692542145</v>
+        <v>946.7796925421447</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="AH84" s="160" t="n">
         <v>1140.017687397478</v>
@@ -8872,13 +8872,13 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>80.63413706293828</v>
+        <v>80.63413706293827</v>
       </c>
       <c r="D85" s="180" t="n">
         <v>41.46195029126793</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>41.61758158889122</v>
+        <v>41.61758158889121</v>
       </c>
       <c r="F85" s="180" t="n">
         <v>40.62070264877642</v>
@@ -8893,16 +8893,16 @@
         <v>39.30503884763295</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>38.693307862986</v>
+        <v>38.69330786298599</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>37.79211035185904</v>
+        <v>37.79211035185903</v>
       </c>
       <c r="L85" s="181" t="n">
         <v>34.89609300366028</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>96456.52564291806</v>
+        <v>96456.52564291804</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>94772.19101135473</v>
@@ -8911,7 +8911,7 @@
         <v>109389.7336532371</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>124667.8800774211</v>
+        <v>124667.880077421</v>
       </c>
       <c r="Q85" s="184" t="n">
         <v>134907.0186081302</v>
@@ -8937,7 +8937,7 @@
         <v>39.05628804417071</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>79.57326141401084</v>
+        <v>79.57326141401083</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>40.94436408540395</v>
@@ -8952,7 +8952,7 @@
         <v>36.3859431407827</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>96456.52564291806</v>
+        <v>96456.52564291804</v>
       </c>
       <c r="AE85" s="189" t="n">
         <v>94772.19101135473</v>
@@ -8961,7 +8961,7 @@
         <v>109389.7336532371</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>124667.8800774211</v>
+        <v>124667.880077421</v>
       </c>
       <c r="AH85" s="190" t="n">
         <v>134907.0186081302</v>
@@ -9877,7 +9877,7 @@
         <v>7.704699476065055</v>
       </c>
       <c r="F95" s="80" t="n">
-        <v>7.903368820239653</v>
+        <v>7.903368820239654</v>
       </c>
       <c r="G95" s="81" t="n">
         <v>8.135930453874115</v>
@@ -9907,7 +9907,7 @@
         <v>7.704699476065055</v>
       </c>
       <c r="P95" s="80" t="n">
-        <v>7.903368820239653</v>
+        <v>7.903368820239654</v>
       </c>
       <c r="Q95" s="81" t="n">
         <v>8.135930453874115</v>
